--- a/results/Int All Data 0.1/Rando_2_permute.xlsx
+++ b/results/Int All Data 0.1/Rando_2_permute.xlsx
@@ -440,1027 +440,1027 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8062988282137209</v>
+        <v>0.8121589709454904</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8015609886685535</v>
+        <v>0.8121589709454904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8020403750539802</v>
+        <v>0.8150128795344107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8013862533909848</v>
+        <v>0.8158193267513351</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8015497838067337</v>
+        <v>0.8169192202142975</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8017021093606627</v>
+        <v>0.8197843336650377</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8008956621437384</v>
+        <v>0.8188367657560041</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8008956621437384</v>
+        <v>0.8217354937922037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8039131011484075</v>
+        <v>0.8210925769910282</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.799327587157169</v>
+        <v>0.8210925769910282</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.799327587157169</v>
+        <v>0.8210925769910282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7985323448020646</v>
+        <v>0.8210925769910282</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8002639502043827</v>
+        <v>0.8204608650516726</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7999480942347048</v>
+        <v>0.8204608650516726</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7946748439950118</v>
+        <v>0.8204608650516726</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7825199915933253</v>
+        <v>0.8218990242079526</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7866709386464164</v>
+        <v>0.8181199574336384</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7841440908889937</v>
+        <v>0.8192758752057001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7847758028283494</v>
+        <v>0.8207140343619801</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.783828234919316</v>
+        <v>0.8222933142103692</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7847870076901692</v>
+        <v>0.8222933142103692</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7830441974260313</v>
+        <v>0.8198963822832359</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.784798212551989</v>
+        <v>0.8205392990844114</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7833488485338893</v>
+        <v>0.8205392990844114</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7852103697664967</v>
+        <v>0.8293317844378399</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.781455832554545</v>
+        <v>0.8287000724984843</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.782893991710825</v>
+        <v>0.8277525045894508</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7710616576290876</v>
+        <v>0.8291682540220912</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7782636582723073</v>
+        <v>0.8269572622343464</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7782748631341271</v>
+        <v>0.8311082092874373</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7787542495195537</v>
+        <v>0.8277973240367302</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7777954767487004</v>
+        <v>0.8268833707131562</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7760302567609227</v>
+        <v>0.8262740684974401</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7741127112192161</v>
+        <v>0.8114736573698615</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7711064770763669</v>
+        <v>0.811146596538364</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7711064770763669</v>
+        <v>0.8051341282526654</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7755844849609557</v>
+        <v>0.8046771515908784</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7755844849609557</v>
+        <v>0.803729583681845</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7755844849609557</v>
+        <v>0.8006270482941658</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7781337424420178</v>
+        <v>0.797434874011928</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7856291893312757</v>
+        <v>0.7956584491623306</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7853133333615978</v>
+        <v>0.7939268437600124</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.786740287656058</v>
+        <v>0.7952126773623633</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7853133333615978</v>
+        <v>0.7952126773623633</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7916976819260734</v>
+        <v>0.7947332909769368</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7929835155284244</v>
+        <v>0.7952126773623633</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7929835155284244</v>
+        <v>0.7958667990253587</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7867514925178778</v>
+        <v>0.8016260980007499</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7842022350368156</v>
+        <v>0.7998944925984317</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7870785533493755</v>
+        <v>0.7973564399791893</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7923405987272488</v>
+        <v>0.7933802282036668</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7923405987272488</v>
+        <v>0.8033240888176085</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7913818259563955</v>
+        <v>0.7995159499693835</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7920135378957511</v>
+        <v>0.8024840270152247</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7910547651248978</v>
+        <v>0.7529597491080022</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.790891234709149</v>
+        <v>0.7595815196094167</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7904118483237224</v>
+        <v>0.7669022312211058</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7921770683115</v>
+        <v>0.765757518310864</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7948898562083111</v>
+        <v>0.7653789756818159</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.783722848651389</v>
+        <v>0.7885663772985865</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7786019239656247</v>
+        <v>0.7916846600596341</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.779560696736478</v>
+        <v>0.803263824831064</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7833957878198912</v>
+        <v>0.8050738642661209</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7826677746357058</v>
+        <v>0.8194285035937323</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7758712688567225</v>
+        <v>0.8203760715027657</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7719174668048399</v>
+        <v>0.8189379123464858</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7741508683162241</v>
+        <v>0.7926413129917647</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7733556259611198</v>
+        <v>0.7856924816588525</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7719174668048399</v>
+        <v>0.7903004053737306</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7757861724737125</v>
+        <v>0.7831880436250696</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7745451583186409</v>
+        <v>0.7935083270293368</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7836647045035671</v>
+        <v>0.7939877134147634</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7820742197933581</v>
+        <v>0.7970454293551632</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7808107959146469</v>
+        <v>0.799780626975614</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7792651306517171</v>
+        <v>0.7980154069878364</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7780017067730058</v>
+        <v>0.8028652951512021</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7792987452371767</v>
+        <v>0.8033446815366287</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8004029510577693</v>
+        <v>0.7918954325954881</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7994889977341952</v>
+        <v>0.793971966041395</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8043052713121015</v>
+        <v>0.7955736556134239</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.8043052713121015</v>
+        <v>0.795770800614632</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8046211272817793</v>
+        <v>0.7879819074793362</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8042940664502816</v>
+        <v>0.7951951129843756</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8019307491086078</v>
+        <v>0.794095219521413</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.804681694102427</v>
+        <v>0.7926794700887727</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.8070226017204611</v>
+        <v>0.8013150873767239</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.8070226017204611</v>
+        <v>0.8038979594432456</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8066843360271436</v>
+        <v>0.7964697417249067</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8234740643788963</v>
+        <v>0.8064762889982187</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8233217388249674</v>
+        <v>0.8001143501573829</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8365943519017074</v>
+        <v>0.7866467119181573</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.8418451924177609</v>
+        <v>0.7871082310914929</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.8559333377345223</v>
+        <v>0.767693233898765</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.8541793226085646</v>
+        <v>0.7440646029935757</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8636819539340875</v>
+        <v>0.7440646029935757</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.86478184739705</v>
+        <v>0.6982206679430114</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.8609019368663575</v>
+        <v>0.7050956077547335</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.8517487760959718</v>
+        <v>0.6734224917311149</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.8545399980255217</v>
+        <v>0.6965629540618836</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.8538119848413361</v>
+        <v>0.701910095822767</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.842158928548716</v>
+        <v>0.7020736262385158</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.842158928548716</v>
+        <v>0.6986955118168896</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.842158928548716</v>
+        <v>0.7031511099778386</v>
       </c>
     </row>
     <row r="105">
@@ -1470,517 +1470,517 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.8424747845183937</v>
+        <v>0.7020176019294166</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.8440943413025137</v>
+        <v>0.6657144553013835</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.8098522835811223</v>
+        <v>0.6431160660154118</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7799692199417468</v>
+        <v>0.6421684981063784</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7206891413986938</v>
+        <v>0.6364942955139973</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7206891413986938</v>
+        <v>0.6364942955139973</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.724315882619079</v>
+        <v>0.6416376299234011</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7085230841351875</v>
+        <v>0.6411582435379745</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6821995325452783</v>
+        <v>0.6429682829730314</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6559834870620186</v>
+        <v>0.6429682829730314</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6670160362771029</v>
+        <v>0.6364091991309873</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6090778156455</v>
+        <v>0.604467469257796</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6176059268268013</v>
+        <v>0.5873415950514485</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6373189127771159</v>
+        <v>0.6071487624078703</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6373189127771159</v>
+        <v>0.603952045614084</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6401616165042163</v>
+        <v>0.6374439832617534</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6568347537262222</v>
+        <v>0.645132032640671</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6631070536724994</v>
+        <v>0.6704565345239963</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5555458312160182</v>
+        <v>0.6754272534945541</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5574409670340852</v>
+        <v>0.6643701747171076</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.554130081783378</v>
+        <v>0.613407737653605</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5492399166842815</v>
+        <v>0.6150206320874536</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5489240607146038</v>
+        <v>0.6319133240343076</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5489240607146038</v>
+        <v>0.6255111082577409</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5216193266302014</v>
+        <v>0.6239318284093518</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.522098713015628</v>
+        <v>0.5900053238235349</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5418229038277625</v>
+        <v>0.5884372488369656</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5452861146323987</v>
+        <v>0.5466346348941201</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.544970258662721</v>
+        <v>0.540380202159934</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5014157494326403</v>
+        <v>0.5394214293890807</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5050536955148452</v>
+        <v>0.5258956470020333</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5050536955148452</v>
+        <v>0.5252751399244975</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5045518994057789</v>
+        <v>0.5227482921670749</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5032548609416081</v>
+        <v>0.523041738413113</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5032548609416081</v>
+        <v>0.523041738413113</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5032548609416081</v>
+        <v>0.523041738413113</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4992562394424461</v>
+        <v>0.5225511471658665</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4995720954121239</v>
+        <v>0.5257769360335637</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5022400638616557</v>
+        <v>0.5194037923309081</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5024035942774046</v>
+        <v>0.5151856161068981</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5052799125899644</v>
+        <v>0.5202841310690226</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5023072930325746</v>
+        <v>0.5202841310690226</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5024596185865037</v>
+        <v>0.5204364566229516</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5024596185865037</v>
+        <v>0.5044374281147548</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5017830871998687</v>
+        <v>0.5011153380022276</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4995833002739437</v>
+        <v>0.4970204152582357</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4997356258278727</v>
+        <v>0.5053156470141467</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4977508511152472</v>
+        <v>0.5069464086600863</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4991553956860676</v>
+        <v>0.51344280584276</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4993077212399966</v>
+        <v>0.5078134226976583</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4993077212399966</v>
+        <v>0.498846202066661</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4972042355589015</v>
+        <v>0.4996414444217655</v>
       </c>
     </row>
   </sheetData>
